--- a/app/content/changhen.xlsx
+++ b/app/content/changhen.xlsx
@@ -928,7 +928,7 @@
         <v>让棋一子</v>
       </c>
       <c r="C2" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D2" t="str">
         <v>赢棋的帝王很多，会输棋的帝王很少。</v>
@@ -951,7 +951,7 @@
         <v>敲打</v>
       </c>
       <c r="C3" t="str">
-        <v>威</v>
+        <v>策</v>
       </c>
       <c r="D3" t="str">
         <v>嫡子违法的把柄，拍在棋盘上。</v>
@@ -974,7 +974,7 @@
         <v>恩宠有加</v>
       </c>
       <c r="C4" t="str">
-        <v>利</v>
+        <v>势</v>
       </c>
       <c r="D4" t="str">
         <v>加九锡，赐几杖，抬起来用。</v>
@@ -997,7 +997,7 @@
         <v>外放夺权</v>
       </c>
       <c r="C5" t="str">
-        <v>理</v>
+        <v>隐</v>
       </c>
       <c r="D5" t="str">
         <v>调离中枢，去边关打仗——离朝堂越远越好。</v>
@@ -1020,7 +1020,7 @@
         <v>急宣回京</v>
       </c>
       <c r="C6" t="str">
-        <v>威</v>
+        <v>器</v>
       </c>
       <c r="D6" t="str">
         <v>金牌令箭，便宜行事。</v>
@@ -1043,7 +1043,7 @@
         <v>以情留之</v>
       </c>
       <c r="C7" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D7" t="str">
         <v>先帝托孤之语，一句一句说给他听。</v>
@@ -1137,7 +1137,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>理,威,情,利,理,威,情</v>
+        <v>策,势,策,策,策,势,策</v>
       </c>
       <c r="I2" t="str">
         <v>h_rang,h_shi,h_yong,h_fang</v>
